--- a/src/nodes/HPC/compressor_stage_6_blade_rotor_coordinates_foil.xlsx
+++ b/src/nodes/HPC/compressor_stage_6_blade_rotor_coordinates_foil.xlsx
@@ -357,7 +357,7 @@
         <v>0.00086995336855904377</v>
       </c>
       <c r="B2">
-        <v>0.00092053318907943035</v>
+        <v>0.000869031949660735</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -365,7 +365,7 @@
         <v>0.0017399067371180875</v>
       </c>
       <c r="B3">
-        <v>0.0013530589466432209</v>
+        <v>0.001282070751768803</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -373,7 +373,7 @@
         <v>0.0026098601056771314</v>
       </c>
       <c r="B4">
-        <v>0.0017110118792088315</v>
+        <v>0.0016249908901257131</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -381,7 +381,7 @@
         <v>0.0034798134742361751</v>
       </c>
       <c r="B5">
-        <v>0.0020173895395830875</v>
+        <v>0.0019192587996096271</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -389,7 +389,7 @@
         <v>0.0043497668427952187</v>
       </c>
       <c r="B6">
-        <v>0.0022815775525399963</v>
+        <v>0.0021736363264682613</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -397,7 +397,7 @@
         <v>0.0052197202113542628</v>
       </c>
       <c r="B7">
-        <v>0.0025089386976695129</v>
+        <v>0.0023931305052469331</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -405,7 +405,7 @@
         <v>0.0060896735799133069</v>
       </c>
       <c r="B8">
-        <v>0.002702631522293835</v>
+        <v>0.0025806910094439361</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -413,7 +413,7 @@
         <v>0.00695962694847235</v>
       </c>
       <c r="B9">
-        <v>0.0028675842635983557</v>
+        <v>0.0027409190531361587</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -421,7 +421,7 @@
         <v>0.0078295803170313934</v>
       </c>
       <c r="B10">
-        <v>0.0030091159780739505</v>
+        <v>0.0028787805328402234</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -429,7 +429,7 @@
         <v>0.0086995336855904375</v>
       </c>
       <c r="B11">
-        <v>0.00313233930957022</v>
+        <v>0.0029990485342530778</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -437,7 +437,7 @@
         <v>0.0095694870541494816</v>
       </c>
       <c r="B12">
-        <v>0.0032399878023171556</v>
+        <v>0.00310427557194598</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -445,7 +445,7 @@
         <v>0.010439440422708526</v>
       </c>
       <c r="B13">
-        <v>0.0033254850147075763</v>
+        <v>0.0031883246868070832</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -453,7 +453,7 @@
         <v>0.01130939379126757</v>
       </c>
       <c r="B14">
-        <v>0.0033849005197956333</v>
+        <v>0.0032475284541467584</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -461,7 +461,7 @@
         <v>0.012179347159826614</v>
       </c>
       <c r="B15">
-        <v>0.0034341979351179661</v>
+        <v>0.0032967870606473281</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -469,7 +469,7 @@
         <v>0.013049300528385656</v>
       </c>
       <c r="B16">
-        <v>0.0034880189929381387</v>
+        <v>0.0033497668648019884</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -477,7 +477,7 @@
         <v>0.0139192538969447</v>
       </c>
       <c r="B17">
-        <v>0.0035358238399449157</v>
+        <v>0.0033966313009754687</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -485,7 +485,7 @@
         <v>0.014789207265503744</v>
       </c>
       <c r="B18">
-        <v>0.0035639996093190778</v>
+        <v>0.0034246755682355791</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -493,7 +493,7 @@
         <v>0.015659160634062787</v>
       </c>
       <c r="B19">
-        <v>0.0035718229657842652</v>
+        <v>0.0034332248485909136</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -501,7 +501,7 @@
         <v>0.016529114002621831</v>
       </c>
       <c r="B20">
-        <v>0.003561792956949833</v>
+        <v>0.003424611819785265</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -509,7 +509,7 @@
         <v>0.017399067371180875</v>
       </c>
       <c r="B21">
-        <v>0.0035364086304251387</v>
+        <v>0.0034011691595624239</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -517,7 +517,7 @@
         <v>0.018269020739739919</v>
       </c>
       <c r="B22">
-        <v>0.0034977238217898362</v>
+        <v>0.0033648139381460994</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -525,7 +525,7 @@
         <v>0.019138974108298963</v>
       </c>
       <c r="B23">
-        <v>0.0034460115185047844</v>
+        <v>0.0033158007956796622</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -533,7 +533,7 @@
         <v>0.020008927476858007</v>
       </c>
       <c r="B24">
-        <v>0.00338109949600114</v>
+        <v>0.0032539687647864012</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -541,7 +541,7 @@
         <v>0.020878880845417051</v>
       </c>
       <c r="B25">
-        <v>0.0033028155297100607</v>
+        <v>0.0031791568780896043</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -549,7 +549,7 @@
         <v>0.021748834213976095</v>
       </c>
       <c r="B26">
-        <v>0.003210913340151297</v>
+        <v>0.0030911349763414254</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -557,7 +557,7 @@
         <v>0.022618787582535139</v>
       </c>
       <c r="B27">
-        <v>0.0031048504281989643</v>
+        <v>0.0029893961328094727</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -565,7 +565,7 @@
         <v>0.023488740951094184</v>
       </c>
       <c r="B28">
-        <v>0.0029840102398157732</v>
+        <v>0.0028733642288902225</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -573,7 +573,7 @@
         <v>0.024358694319653228</v>
       </c>
       <c r="B29">
-        <v>0.0028477762209644336</v>
+        <v>0.0027424631459801508</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -581,7 +581,7 @@
         <v>0.025228647688212272</v>
       </c>
       <c r="B30">
-        <v>0.0026958619981501922</v>
+        <v>0.0025964248579019881</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -589,7 +589,7 @@
         <v>0.026098601056771312</v>
       </c>
       <c r="B31">
-        <v>0.0025293019200484457</v>
+        <v>0.0024362137081834967</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -597,7 +597,7 @@
         <v>0.026968554425330356</v>
       </c>
       <c r="B32">
-        <v>0.0023494605158771286</v>
+        <v>0.0022631021327786912</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -605,7 +605,7 @@
         <v>0.0278385077938894</v>
       </c>
       <c r="B33">
-        <v>0.0021577023148541758</v>
+        <v>0.0020783625676415907</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -613,7 +613,7 @@
         <v>0.028708461162448445</v>
       </c>
       <c r="B34">
-        <v>0.0019548559863489688</v>
+        <v>0.0018827672308672377</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -621,7 +621,7 @@
         <v>0.029578414531007489</v>
       </c>
       <c r="B35">
-        <v>0.0017396067603366813</v>
+        <v>0.0016750874691147824</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -629,7 +629,7 @@
         <v>0.030448367899566529</v>
       </c>
       <c r="B36">
-        <v>0.0015101040069439352</v>
+        <v>0.001453594411184402</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -637,7 +637,7 @@
         <v>0.031318321268125573</v>
       </c>
       <c r="B37">
-        <v>0.0012644970962973488</v>
+        <v>0.0012165591858762711</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -645,7 +645,7 @@
         <v>0.032188274636684618</v>
       </c>
       <c r="B38">
-        <v>0.000999622659715654</v>
+        <v>0.00096102762219572684</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -653,7 +653,7 @@
         <v>0.033058228005243662</v>
       </c>
       <c r="B39">
-        <v>0.00070706637328601636</v>
+        <v>0.0006791443499687453</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -661,7 +661,7 @@
         <v>0.033928181373802706</v>
       </c>
       <c r="B40">
-        <v>0.00037710117428771118</v>
+        <v>0.00036182869922646223</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -685,7 +685,7 @@
         <v>0.033928181373802706</v>
       </c>
       <c r="B43">
-        <v>-8.1073077549756507E-05</v>
+        <v>-6.5800602488507516E-05</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -693,7 +693,7 @@
         <v>0.033058228005243662</v>
       </c>
       <c r="B44">
-        <v>-0.00013059432623211409</v>
+        <v>-0.00010267230291484303</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -701,7 +701,7 @@
         <v>0.032188274636684618</v>
       </c>
       <c r="B45">
-        <v>-0.00015822846588215502</v>
+        <v>-0.00011963342836222802</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -709,7 +709,7 @@
         <v>0.031318321268125573</v>
       </c>
       <c r="B46">
-        <v>-0.00017364021633497749</v>
+        <v>-0.00012570230591389995</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -717,7 +717,7 @@
         <v>0.030448367899566529</v>
       </c>
       <c r="B47">
-        <v>-0.00018518386584204415</v>
+        <v>-0.00012867427008251151</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -725,7 +725,7 @@
         <v>0.029578414531007489</v>
       </c>
       <c r="B48">
-        <v>-0.00019597197632027509</v>
+        <v>-0.00013145268509837647</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -733,7 +733,7 @@
         <v>0.028708461162448445</v>
       </c>
       <c r="B49">
-        <v>-0.00020780667810295491</v>
+        <v>-0.000135717922621224</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -741,7 +741,7 @@
         <v>0.0278385077938894</v>
       </c>
       <c r="B50">
-        <v>-0.00022249010152336813</v>
+        <v>-0.0001431503543107832</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -749,7 +749,7 @@
         <v>0.026968554425330356</v>
       </c>
       <c r="B51">
-        <v>-0.00024129097707598719</v>
+        <v>-0.00015493259397754986</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -757,7 +757,7 @@
         <v>0.026098601056771312</v>
       </c>
       <c r="B52">
-        <v>-0.00026334443590003638</v>
+        <v>-0.00017025622403508687</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -765,7 +765,7 @@
         <v>0.025228647688212272</v>
       </c>
       <c r="B53">
-        <v>-0.00028725220929592759</v>
+        <v>-0.00018781506904772362</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -773,7 +773,7 @@
         <v>0.024358694319653228</v>
       </c>
       <c r="B54">
-        <v>-0.00031161602856407333</v>
+        <v>-0.00020630295357978979</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -781,7 +781,7 @@
         <v>0.023488740951094184</v>
       </c>
       <c r="B55">
-        <v>-0.00033537008795076362</v>
+        <v>-0.00022472407702521239</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -789,7 +789,7 @@
         <v>0.022618787582535139</v>
       </c>
       <c r="B56">
-        <v>-0.00035877843348580105</v>
+        <v>-0.00024332413809630883</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -797,7 +797,7 @@
         <v>0.021748834213976095</v>
       </c>
       <c r="B57">
-        <v>-0.00038243757414486616</v>
+        <v>-0.000262659210334994</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -805,7 +805,7 @@
         <v>0.020878880845417051</v>
       </c>
       <c r="B58">
-        <v>-0.00040694401890363952</v>
+        <v>-0.00028328536728318264</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -813,7 +813,7 @@
         <v>0.020008927476858007</v>
       </c>
       <c r="B59">
-        <v>-0.00043282244044103431</v>
+        <v>-0.00030569170922629496</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -821,7 +821,7 @@
         <v>0.019138974108298963</v>
       </c>
       <c r="B60">
-        <v>-0.00046031016624889309</v>
+        <v>-0.00033009944342377023</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -829,7 +829,7 @@
         <v>0.018269020739739919</v>
       </c>
       <c r="B61">
-        <v>-0.00048957268752229059</v>
+        <v>-0.0003566628038785528</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -837,7 +837,7 @@
         <v>0.017399067371180875</v>
       </c>
       <c r="B62">
-        <v>-0.00052077549545630187</v>
+        <v>-0.000385536024593587</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -845,7 +845,7 @@
         <v>0.016529114002621831</v>
       </c>
       <c r="B63">
-        <v>-0.00055364115798722856</v>
+        <v>-0.00041646002082265963</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -853,7 +853,7 @@
         <v>0.015659160634062787</v>
       </c>
       <c r="B64">
-        <v>-0.00058612055001627935</v>
+        <v>-0.00044752243282292762</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -861,7 +861,7 @@
         <v>0.014789207265503744</v>
       </c>
       <c r="B65">
-        <v>-0.00061572162318588924</v>
+        <v>-0.00047639758210239026</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -869,7 +869,7 @@
         <v>0.0139192538969447</v>
       </c>
       <c r="B66">
-        <v>-0.000639952329138494</v>
+        <v>-0.00050075979016904677</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -877,7 +877,7 @@
         <v>0.013049300528385656</v>
       </c>
       <c r="B67">
-        <v>-0.000659544851146372</v>
+        <v>-0.00052129272301022149</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -885,7 +885,7 @@
         <v>0.012179347159826614</v>
       </c>
       <c r="B68">
-        <v>-0.00068812829900117623</v>
+        <v>-0.000550717424530538</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -893,7 +893,7 @@
         <v>0.01130939379126757</v>
       </c>
       <c r="B69">
-        <v>-0.0007362614496706115</v>
+        <v>-0.00059888938402173663</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -901,7 +901,7 @@
         <v>0.010439440422708526</v>
       </c>
       <c r="B70">
-        <v>-0.00078932482230721526</v>
+        <v>-0.00065216449440672216</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -909,7 +909,7 @@
         <v>0.0095694870541494816</v>
       </c>
       <c r="B71">
-        <v>-0.00083137910881812621</v>
+        <v>-0.00069566687844695</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -917,7 +917,7 @@
         <v>0.0086995336855904375</v>
       </c>
       <c r="B72">
-        <v>-0.00086638394994405276</v>
+        <v>-0.00073309317462691014</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -925,7 +925,7 @@
         <v>0.0078295803170313934</v>
       </c>
       <c r="B73">
-        <v>-0.00090094737893786951</v>
+        <v>-0.00077061193370414215</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -933,7 +933,7 @@
         <v>0.00695962694847235</v>
       </c>
       <c r="B74">
-        <v>-0.00093237205026754782</v>
+        <v>-0.00080570683980535091</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -941,7 +941,7 @@
         <v>0.0060896735799133069</v>
       </c>
       <c r="B75">
-        <v>-0.00095558386320313449</v>
+        <v>-0.00083364335035323548</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -949,7 +949,7 @@
         <v>0.0052197202113542628</v>
       </c>
       <c r="B76">
-        <v>-0.0009653070750078839</v>
+        <v>-0.00084949888258530385</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -957,7 +957,7 @@
         <v>0.0043497668427952187</v>
       </c>
       <c r="B77">
-        <v>-0.00095665922961205463</v>
+        <v>-0.00084871800354031945</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -965,7 +965,7 @@
         <v>0.0034798134742361751</v>
       </c>
       <c r="B78">
-        <v>-0.000926532659620716</v>
+        <v>-0.00082840191964725579</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -973,7 +973,7 @@
         <v>0.0026098601056771314</v>
       </c>
       <c r="B79">
-        <v>-0.00086961779328471585</v>
+        <v>-0.00078359680420159747</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -981,7 +981,7 @@
         <v>0.0017399067371180875</v>
       </c>
       <c r="B80">
-        <v>-0.00077658689958931754</v>
+        <v>-0.00070559870471489949</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -989,7 +989,7 @@
         <v>0.00086995336855904377</v>
       </c>
       <c r="B81">
-        <v>-0.00062450399348143123</v>
+        <v>-0.00057300275406273584</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1023,7 +1023,7 @@
         <v>0.0010074303821663944</v>
       </c>
       <c r="B2">
-        <v>0.00046198032410749423</v>
+        <v>0.00035910153348066211</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -1031,7 +1031,7 @@
         <v>0.0020148607643327887</v>
       </c>
       <c r="B3">
-        <v>0.00068764254183258263</v>
+        <v>0.00054583664123884106</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -1039,7 +1039,7 @@
         <v>0.0030222911464991833</v>
       </c>
       <c r="B4">
-        <v>0.00087646313949370637</v>
+        <v>0.000704627754068349</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -1047,7 +1047,7 @@
         <v>0.0040297215286655775</v>
       </c>
       <c r="B5">
-        <v>0.0010395288278054532</v>
+        <v>0.00084350302404351621</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -1055,7 +1055,7 @@
         <v>0.0050371519108319716</v>
       </c>
       <c r="B6">
-        <v>0.001181359013607959</v>
+        <v>0.0009657357990527297</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -1063,7 +1063,7 @@
         <v>0.0060445822929983666</v>
       </c>
       <c r="B7">
-        <v>0.0013045328071118649</v>
+        <v>0.0010731945535942316</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -1071,7 +1071,7 @@
         <v>0.0070520126751647608</v>
       </c>
       <c r="B8">
-        <v>0.0014105661325629249</v>
+        <v>0.001166977965908836</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -1079,7 +1079,7 @@
         <v>0.0080594430573311549</v>
       </c>
       <c r="B9">
-        <v>0.0015018296432510138</v>
+        <v>0.0012488034284661022</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -1087,7 +1087,7 @@
         <v>0.0090668734394975491</v>
       </c>
       <c r="B10">
-        <v>0.0015808829683366095</v>
+        <v>0.0013205250986464264</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -1095,7 +1095,7 @@
         <v>0.010074303821663943</v>
       </c>
       <c r="B11">
-        <v>0.0016501869114184686</v>
+        <v>0.0013839254792448075</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -1103,7 +1103,7 @@
         <v>0.011081734203830339</v>
       </c>
       <c r="B12">
-        <v>0.0017110547101681565</v>
+        <v>0.0014399561833861323</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -1111,7 +1111,7 @@
         <v>0.012089164585996733</v>
       </c>
       <c r="B13">
-        <v>0.0017603081641101863</v>
+        <v>0.0014863169201002392</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -1119,7 +1119,7 @@
         <v>0.013096594968163127</v>
       </c>
       <c r="B14">
-        <v>0.0017960461853513935</v>
+        <v>0.0015216319743657106</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -1127,7 +1127,7 @@
         <v>0.014104025350329522</v>
       </c>
       <c r="B15">
-        <v>0.0018259675744749537</v>
+        <v>0.0015514758390511464</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -1135,7 +1135,7 @@
         <v>0.015111455732495914</v>
       </c>
       <c r="B16">
-        <v>0.0018571336338177162</v>
+        <v>0.0015809614114639795</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -1143,7 +1143,7 @@
         <v>0.01611888611466231</v>
       </c>
       <c r="B17">
-        <v>0.0018844557842548813</v>
+        <v>0.0016064049987769566</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -1151,7 +1151,7 @@
         <v>0.017126316496828706</v>
       </c>
       <c r="B18">
-        <v>0.0019013631046273349</v>
+        <v>0.0016230496307440196</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -1159,7 +1159,7 @@
         <v>0.018133746878995098</v>
       </c>
       <c r="B19">
-        <v>0.0019075051871003564</v>
+        <v>0.0016306418175785758</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -1167,7 +1167,7 @@
         <v>0.019141177261161494</v>
       </c>
       <c r="B20">
-        <v>0.0019040867521703236</v>
+        <v>0.0016300539396088985</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -1175,7 +1175,7 @@
         <v>0.020148607643327886</v>
       </c>
       <c r="B21">
-        <v>0.0018923125203336138</v>
+        <v>0.0016221583771632618</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -1183,7 +1183,7 @@
         <v>0.021156038025494282</v>
       </c>
       <c r="B22">
-        <v>0.0018731727514578168</v>
+        <v>0.0016076721878605631</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -1191,7 +1191,7 @@
         <v>0.022163468407660678</v>
       </c>
       <c r="B23">
-        <v>0.0018467998628953685</v>
+        <v>0.0015866911384821954</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -1199,7 +1199,7 @@
         <v>0.023170898789827071</v>
       </c>
       <c r="B24">
-        <v>0.0018131118113699173</v>
+        <v>0.0015591556731001765</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -1207,7 +1207,7 @@
         <v>0.024178329171993466</v>
       </c>
       <c r="B25">
-        <v>0.0017720265536051113</v>
+        <v>0.0015250062357865231</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -1215,7 +1215,7 @@
         <v>0.025185759554159859</v>
       </c>
       <c r="B26">
-        <v>0.0017234266634815554</v>
+        <v>0.0014841576021714091</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -1223,7 +1223,7 @@
         <v>0.026193189936326255</v>
       </c>
       <c r="B27">
-        <v>0.0016670531835076795</v>
+        <v>0.0014364218741176329</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -1231,7 +1231,7 @@
         <v>0.027200620318492647</v>
       </c>
       <c r="B28">
-        <v>0.0016026117733488703</v>
+        <v>0.0013815854850461507</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -1239,7 +1239,7 @@
         <v>0.028208050700659043</v>
       </c>
       <c r="B29">
-        <v>0.0015298080926705151</v>
+        <v>0.0013194348683779173</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -1247,7 +1247,7 @@
         <v>0.029215481082825439</v>
       </c>
       <c r="B30">
-        <v>0.0014485074801262039</v>
+        <v>0.0012498720133375667</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -1255,7 +1255,7 @@
         <v>0.030222911464991828</v>
       </c>
       <c r="B31">
-        <v>0.0013592139903223464</v>
+        <v>0.0011732611323644491</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -1263,7 +1263,7 @@
         <v>0.031230341847158224</v>
       </c>
       <c r="B32">
-        <v>0.0012625913568535541</v>
+        <v>0.0010900819937015916</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -1271,7 +1271,7 @@
         <v>0.03223777222932462</v>
       </c>
       <c r="B33">
-        <v>0.0011593033133144397</v>
+        <v>0.0010008143655920224</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -1279,7 +1279,7 @@
         <v>0.033245202611491012</v>
       </c>
       <c r="B34">
-        <v>0.0010497554327003852</v>
+        <v>0.00090575105405893311</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -1287,7 +1287,7 @@
         <v>0.034252632993657411</v>
       </c>
       <c r="B35">
-        <v>0.00093332064560984994</v>
+        <v>0.00080443701624616931</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -1295,7 +1295,7 @@
         <v>0.035260063375823804</v>
       </c>
       <c r="B36">
-        <v>0.00080911372204206283</v>
+        <v>0.00069623024707774037</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -1303,7 +1303,7 @@
         <v>0.036267493757990196</v>
       </c>
       <c r="B37">
-        <v>0.00067624943199625146</v>
+        <v>0.00058048874147765422</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -1311,7 +1311,7 @@
         <v>0.037274924140156589</v>
       </c>
       <c r="B38">
-        <v>0.0005332095141119984</v>
+        <v>0.00045611213103803042</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -1319,7 +1319,7 @@
         <v>0.038282354522322988</v>
       </c>
       <c r="B39">
-        <v>0.00037594358159029958</v>
+        <v>0.000320166594023428</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -1327,7 +1327,7 @@
         <v>0.03928978490448938</v>
       </c>
       <c r="B40">
-        <v>0.00019976821627250472</v>
+        <v>0.00016925994536651595</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -1343,7 +1343,7 @@
         <v>0.040297215286655773</v>
       </c>
       <c r="B42">
-        <v>-3.5795486024453546E-17</v>
+        <v>-3.5786747958781761E-17</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -1351,7 +1351,7 @@
         <v>0.03928978490448938</v>
       </c>
       <c r="B43">
-        <v>-2.1306210582486079E-05</v>
+        <v>9.2020603235026536E-06</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -1359,7 +1359,7 @@
         <v>0.038282354522322988</v>
       </c>
       <c r="B44">
-        <v>-2.8237487734857067E-05</v>
+        <v>2.7539499832014548E-05</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -1367,7 +1367,7 @@
         <v>0.037274924140156589</v>
       </c>
       <c r="B45">
-        <v>-2.5467174829798664E-05</v>
+        <v>5.16302082441693E-05</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -1375,7 +1375,7 @@
         <v>0.036267493757990196</v>
       </c>
       <c r="B46">
-        <v>-1.766861523996092E-05</v>
+        <v>7.8092075278636362E-05</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -1383,7 +1383,7 @@
         <v>0.035260063375823804</v>
       </c>
       <c r="B47">
-        <v>-8.8824733515787629E-06</v>
+        <v>0.00010400100161274375</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -1391,7 +1391,7 @@
         <v>0.034252632993657411</v>
       </c>
       <c r="B48">
-        <v>-6.186976052266964E-07</v>
+        <v>0.00012826493175845387</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -1399,7 +1399,7 @@
         <v>0.033245202611491012</v>
       </c>
       <c r="B49">
-        <v>6.2454425449359931E-06</v>
+        <v>0.000150249821186388</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -1407,7 +1407,7 @@
         <v>0.03223777222932462</v>
       </c>
       <c r="B50">
-        <v>1.0832677644749913E-05</v>
+        <v>0.0001693216253671671</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -1415,7 +1415,7 @@
         <v>0.031230341847158224</v>
       </c>
       <c r="B51">
-        <v>1.2523507926290027E-05</v>
+        <v>0.00018503287107825243</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -1423,7 +1423,7 @@
         <v>0.030222911464991828</v>
       </c>
       <c r="B52">
-        <v>1.1729512366568583E-05</v>
+        <v>0.00019768237032446591</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -1431,7 +1431,7 @@
         <v>0.029215481082825439</v>
       </c>
       <c r="B53">
-        <v>9.1200396288321515E-06</v>
+        <v>0.00020775550641746943</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -1439,7 +1439,7 @@
         <v>0.028208050700659043</v>
       </c>
       <c r="B54">
-        <v>5.3644383763272843E-06</v>
+        <v>0.00021573766266892513</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -1447,7 +1447,7 @@
         <v>0.027200620318492647</v>
       </c>
       <c r="B55">
-        <v>9.7200303930534742E-07</v>
+        <v>0.00022199829134202532</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -1455,7 +1455,7 @@
         <v>0.026193189936326255</v>
       </c>
       <c r="B56">
-        <v>-4.18818888396307E-06</v>
+        <v>0.0002264431205060836</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -1463,7 +1463,7 @@
         <v>0.025185759554159859</v>
       </c>
       <c r="B57">
-        <v>-1.040711412820261E-05</v>
+        <v>0.00022886194718194403</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -1471,7 +1471,7 @@
         <v>0.024178329171993466</v>
       </c>
       <c r="B58">
-        <v>-1.7975749428137857E-05</v>
+        <v>0.00022904456839045054</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -1479,7 +1479,7 @@
         <v>0.023170898789827071</v>
       </c>
       <c r="B59">
-        <v>-2.7150060149943426E-05</v>
+        <v>0.00022680607811979733</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -1487,7 +1487,7 @@
         <v>0.022163468407660678</v>
       </c>
       <c r="B60">
-        <v>-3.80459661855935E-05</v>
+        <v>0.0002220627582275792</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -1495,7 +1495,7 @@
         <v>0.021156038025494282</v>
       </c>
       <c r="B61">
-        <v>-5.07443760585122E-05</v>
+        <v>0.00021475618753874113</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -1503,7 +1503,7 @@
         <v>0.020148607643327886</v>
       </c>
       <c r="B62">
-        <v>-6.5326198292123651E-05</v>
+        <v>0.00020482794487822802</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -1511,7 +1511,7 @@
         <v>0.019141177261161494</v>
       </c>
       <c r="B63">
-        <v>-8.165826639072584E-05</v>
+        <v>0.00019237454617069888</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -1519,7 +1519,7 @@
         <v>0.018133746878995098</v>
       </c>
       <c r="B64">
-        <v>-9.87511137821123E-05</v>
+        <v>0.00017811225573966831</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -1527,7 +1527,7 @@
         <v>0.017126316496828706</v>
       </c>
       <c r="B65">
-        <v>-0.00011540119887495041</v>
+        <v>0.00016291227500836493</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -1535,7 +1535,7 @@
         <v>0.01611888611466231</v>
       </c>
       <c r="B66">
-        <v>-0.00013040498007790754</v>
+        <v>0.00014764580540001731</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -1543,7 +1543,7 @@
         <v>0.015111455732495914</v>
       </c>
       <c r="B67">
-        <v>-0.00014411435425284197</v>
+        <v>0.00013205786810089503</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -1551,7 +1551,7 @@
         <v>0.014104025350329522</v>
       </c>
       <c r="B68">
-        <v>-0.00016310297207437557</v>
+        <v>0.00011138876334943184</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -1559,7 +1559,7 @@
         <v>0.013096594968163127</v>
       </c>
       <c r="B69">
-        <v>-0.00019246258990717775</v>
+        <v>8.19516210785051E-05</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -1567,7 +1567,7 @@
         <v>0.012089164585996733</v>
       </c>
       <c r="B70">
-        <v>-0.00022513563306334367</v>
+        <v>4.8855610946603528E-05</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -1575,7 +1575,7 @@
         <v>0.011081734203830339</v>
       </c>
       <c r="B71">
-        <v>-0.00025342736796245469</v>
+        <v>1.7671158819569662E-05</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -1583,7 +1583,7 @@
         <v>0.010074303821663943</v>
       </c>
       <c r="B72">
-        <v>-0.00027924375650660989</v>
+        <v>-1.2982324332949102E-05</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -1591,7 +1591,7 @@
         <v>0.0090668734394975491</v>
       </c>
       <c r="B73">
-        <v>-0.00030576826130239491</v>
+        <v>-4.54103916122124E-05</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -1599,7 +1599,7 @@
         <v>0.0080594430573311549</v>
       </c>
       <c r="B74">
-        <v>-0.00033169365229182416</v>
+        <v>-7.8667437506912586E-05</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -1607,7 +1607,7 @@
         <v>0.0070520126751647608</v>
       </c>
       <c r="B75">
-        <v>-0.0003545655098580084</v>
+        <v>-0.00011097734320391968</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -1615,7 +1615,7 @@
         <v>0.0060445822929983666</v>
       </c>
       <c r="B76">
-        <v>-0.00037183134881301513</v>
+        <v>-0.00014049309529538169</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1623,7 +1623,7 @@
         <v>0.0050371519108319716</v>
       </c>
       <c r="B77">
-        <v>-0.00038112804838645619</v>
+        <v>-0.00016550483383122688</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1631,7 +1631,7 @@
         <v>0.0040297215286655775</v>
       </c>
       <c r="B78">
-        <v>-0.00038094801104916266</v>
+        <v>-0.00018492220728722562</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1639,7 +1639,7 @@
         <v>0.0030222911464991833</v>
       </c>
       <c r="B79">
-        <v>-0.00036872081286395709</v>
+        <v>-0.00019688542743859959</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1647,7 +1647,7 @@
         <v>0.0020148607643327887</v>
       </c>
       <c r="B80">
-        <v>-0.00033993644797713937</v>
+        <v>-0.00019813054738339778</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1655,7 +1655,7 @@
         <v>0.0010074303821663944</v>
       </c>
       <c r="B81">
-        <v>-0.00028351815869563754</v>
+        <v>-0.0001806393680688054</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1689,7 +1689,7 @@
         <v>0.001130939379126757</v>
       </c>
       <c r="B2">
-        <v>0.00031454054283242081</v>
+        <v>0.0002308510287770408</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -1697,7 +1697,7 @@
         <v>0.0022618787582535139</v>
       </c>
       <c r="B3">
-        <v>0.000469747001765115</v>
+        <v>0.00035439118509418582</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -1705,7 +1705,7 @@
         <v>0.0033928181373802714</v>
       </c>
       <c r="B4">
-        <v>0.00059997647502219812</v>
+        <v>0.00046019236776213092</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -1713,7 +1713,7 @@
         <v>0.0045237575165070279</v>
       </c>
       <c r="B5">
-        <v>0.00071269458035271981</v>
+        <v>0.00055323212789584709</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -1721,7 +1721,7 @@
         <v>0.0056546968956337849</v>
       </c>
       <c r="B6">
-        <v>0.00081094357861835934</v>
+        <v>0.00063553908625179</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -1729,7 +1729,7 @@
         <v>0.0067856362747605427</v>
       </c>
       <c r="B7">
-        <v>0.000896458967026256</v>
+        <v>0.00070827065433956343</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -1737,7 +1737,7 @@
         <v>0.0079165756538872988</v>
       </c>
       <c r="B8">
-        <v>0.00097026019490827834</v>
+        <v>0.0007721068615271923</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -1745,7 +1745,7 @@
         <v>0.0090475150330140558</v>
       </c>
       <c r="B9">
-        <v>0.0010339425772091131</v>
+        <v>0.00082811161020804314</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -1753,7 +1753,7 @@
         <v>0.010178454412140813</v>
       </c>
       <c r="B10">
-        <v>0.0010892287910864106</v>
+        <v>0.00087743369258160367</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -1761,7 +1761,7 @@
         <v>0.01130939379126757</v>
       </c>
       <c r="B11">
-        <v>0.001137775096936861</v>
+        <v>0.00092117758704650464</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -1769,7 +1769,7 @@
         <v>0.012440333170394329</v>
       </c>
       <c r="B12">
-        <v>0.0011804648752281313</v>
+        <v>0.00095993250087497012</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -1777,7 +1777,7 @@
         <v>0.013571272549521085</v>
       </c>
       <c r="B13">
-        <v>0.001215156403472757</v>
+        <v>0.00099227087063445576</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -1785,7 +1785,7 @@
         <v>0.014702211928647841</v>
       </c>
       <c r="B14">
-        <v>0.0012405682449444567</v>
+        <v>0.0010173386382650348</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -1793,7 +1793,7 @@
         <v>0.015833151307774598</v>
       </c>
       <c r="B15">
-        <v>0.0012618852089168087</v>
+        <v>0.0010385925379020216</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -1801,7 +1801,7 @@
         <v>0.016964090686901356</v>
       </c>
       <c r="B16">
-        <v>0.0012838627778234</v>
+        <v>0.0010592030696021555</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -1809,7 +1809,7 @@
         <v>0.018095030066028112</v>
       </c>
       <c r="B17">
-        <v>0.0013030728807379879</v>
+        <v>0.0010768850049126366</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -1817,7 +1817,7 @@
         <v>0.01922596944515487</v>
       </c>
       <c r="B18">
-        <v>0.0013150890887051027</v>
+        <v>0.0010886875219444168</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -1825,7 +1825,7 @@
         <v>0.020356908824281626</v>
       </c>
       <c r="B19">
-        <v>0.001319675094012196</v>
+        <v>0.0010944531535729998</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -1833,7 +1833,7 @@
         <v>0.021487848203408384</v>
       </c>
       <c r="B20">
-        <v>0.0013176421192574502</v>
+        <v>0.0010947227713650259</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -1841,7 +1841,7 @@
         <v>0.022618787582535139</v>
       </c>
       <c r="B21">
-        <v>0.0013098013870390477</v>
+        <v>0.0010900372468871363</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -1849,7 +1849,7 @@
         <v>0.023749726961661898</v>
       </c>
       <c r="B22">
-        <v>0.0012968197425242193</v>
+        <v>0.0010808411816031456</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -1857,7 +1857,7 @@
         <v>0.024880666340788657</v>
       </c>
       <c r="B23">
-        <v>0.0012787865211563937</v>
+        <v>0.0010671940965655694</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -1865,7 +1865,7 @@
         <v>0.026011605719915412</v>
       </c>
       <c r="B24">
-        <v>0.0012556466809480482</v>
+        <v>0.0010490592427240969</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -1873,7 +1873,7 @@
         <v>0.027142545099042171</v>
       </c>
       <c r="B25">
-        <v>0.0012273451799116601</v>
+        <v>0.0010263998710284177</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -1881,7 +1881,7 @@
         <v>0.028273484478168923</v>
       </c>
       <c r="B26">
-        <v>0.0011938032153998792</v>
+        <v>0.00099916337420883684</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -1889,7 +1889,7 @@
         <v>0.029404423857295681</v>
       </c>
       <c r="B27">
-        <v>0.0011548469421260416</v>
+        <v>0.000967233712118117</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -1897,7 +1897,7 @@
         <v>0.03053536323642244</v>
       </c>
       <c r="B28">
-        <v>0.0011102787541436576</v>
+        <v>0.000930478986389637</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -1905,7 +1905,7 @@
         <v>0.031666302615549195</v>
       </c>
       <c r="B29">
-        <v>0.0010599010455062355</v>
+        <v>0.00088876729865677482</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -1913,7 +1913,7 @@
         <v>0.032797241994675957</v>
       </c>
       <c r="B30">
-        <v>0.0010036238361796424</v>
+        <v>0.00084203848327631114</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -1921,7 +1921,7 @@
         <v>0.033928181373802713</v>
       </c>
       <c r="B31">
-        <v>0.00094178764977917732</v>
+        <v>0.00079051930549863447</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -1929,7 +1929,7 @@
         <v>0.035059120752929468</v>
       </c>
       <c r="B32">
-        <v>0.00087484063583249591</v>
+        <v>0.00073450826329753539</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -1937,7 +1937,7 @@
         <v>0.036190060132056223</v>
       </c>
       <c r="B33">
-        <v>0.00080323094386725469</v>
+        <v>0.0006743038546468044</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -1945,7 +1945,7 @@
         <v>0.037320999511182985</v>
       </c>
       <c r="B34">
-        <v>0.00072723291325347021</v>
+        <v>0.00061008868559565756</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -1953,7 +1953,7 @@
         <v>0.038451938890309741</v>
       </c>
       <c r="B35">
-        <v>0.00064642564273059819</v>
+        <v>0.00054158179449501293</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -1961,7 +1961,7 @@
         <v>0.039582878269436496</v>
       </c>
       <c r="B36">
-        <v>0.00056021442088045469</v>
+        <v>0.00046838632777121409</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -1969,7 +1969,7 @@
         <v>0.040713817648563251</v>
       </c>
       <c r="B37">
-        <v>0.00046800453628485479</v>
+        <v>0.00039010543185060369</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -1977,7 +1977,7 @@
         <v>0.041844757027690013</v>
       </c>
       <c r="B38">
-        <v>0.00036877496280554876</v>
+        <v>0.00030605802683566737</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -1985,7 +1985,7 @@
         <v>0.042975696406816769</v>
       </c>
       <c r="B39">
-        <v>0.00025979941542402343</v>
+        <v>0.00021442612753345798</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -1993,7 +1993,7 @@
         <v>0.044106635785943524</v>
       </c>
       <c r="B40">
-        <v>0.00013792529440169994</v>
+        <v>0.00011310752242717041</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -2009,7 +2009,7 @@
         <v>0.045237575165070279</v>
       </c>
       <c r="B42">
-        <v>-2.4523338635972749E-21</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -2017,7 +2017,7 @@
         <v>0.044106635785943524</v>
       </c>
       <c r="B43">
-        <v>-1.09813374454771E-05</v>
+        <v>1.3836434529052423E-05</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -2025,7 +2025,7 @@
         <v>0.042975696406816769</v>
       </c>
       <c r="B44">
-        <v>-1.2440311919369006E-05</v>
+        <v>3.293297597119642E-05</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -2033,7 +2033,7 @@
         <v>0.041844757027690013</v>
       </c>
       <c r="B45">
-        <v>-7.5266530137392294E-06</v>
+        <v>5.5190282956142117E-05</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -2041,7 +2041,7 @@
         <v>0.040713817648563251</v>
       </c>
       <c r="B46">
-        <v>6.0990967934865362E-07</v>
+        <v>7.85090141135997E-05</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -2049,7 +2049,7 @@
         <v>0.039582878269436496</v>
       </c>
       <c r="B47">
-        <v>9.2458622250114243E-06</v>
+        <v>0.00010107395533425197</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -2057,7 +2057,7 @@
         <v>0.038451938890309741</v>
       </c>
       <c r="B48">
-        <v>1.7362553317087285E-05</v>
+        <v>0.00012220640155267246</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -2065,7 +2065,7 @@
         <v>0.037320999511182985</v>
       </c>
       <c r="B49">
-        <v>2.4367547306594907E-05</v>
+        <v>0.00014151177496440749</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -2073,7 +2073,7 @@
         <v>0.036190060132056223</v>
       </c>
       <c r="B50">
-        <v>2.9668408544552854E-05</v>
+        <v>0.00015859549776500319</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -2081,7 +2081,7 @@
         <v>0.035059120752929468</v>
       </c>
       <c r="B51">
-        <v>3.2846400622733017E-05</v>
+        <v>0.00017317877315769351</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -2089,7 +2089,7 @@
         <v>0.033928181373802713</v>
       </c>
       <c r="B52">
-        <v>3.4177584095920463E-05</v>
+        <v>0.00018544592837646331</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -2097,7 +2097,7 @@
         <v>0.032797241994675957</v>
       </c>
       <c r="B53">
-        <v>3.4111718759653554E-05</v>
+        <v>0.00019569707166298511</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -2105,7 +2105,7 @@
         <v>0.031666302615549195</v>
       </c>
       <c r="B54">
-        <v>3.3098564409470658E-05</v>
+        <v>0.00020423231125893152</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -2113,7 +2113,7 @@
         <v>0.03053536323642244</v>
       </c>
       <c r="B55">
-        <v>3.1480147619532948E-05</v>
+        <v>0.00021127991537355379</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -2121,7 +2121,7 @@
         <v>0.029404423857295681</v>
       </c>
       <c r="B56">
-        <v>2.9167562078492935E-05</v>
+        <v>0.00021678079208641783</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -2129,7 +2129,7 @@
         <v>0.028273484478168923</v>
       </c>
       <c r="B57">
-        <v>2.5964168253625927E-05</v>
+        <v>0.0002206040094446682</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -2137,7 +2137,7 @@
         <v>0.027142545099042171</v>
       </c>
       <c r="B58">
-        <v>2.1673326612207278E-05</v>
+        <v>0.00022261863549544951</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -2145,7 +2145,7 @@
         <v>0.026011605719915412</v>
       </c>
       <c r="B59">
-        <v>1.6122051604341279E-05</v>
+        <v>0.00022270948982829251</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -2153,7 +2153,7 @@
         <v>0.024880666340788657</v>
       </c>
       <c r="B60">
-        <v>9.2319736114483447E-06</v>
+        <v>0.00022082439820227267</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -2161,7 +2161,7 @@
         <v>0.023749726961661898</v>
       </c>
       <c r="B61">
-        <v>9.4837699777790234E-07</v>
+        <v>0.00021692693791885157</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -2169,7 +2169,7 @@
         <v>0.022618787582535139</v>
       </c>
       <c r="B62">
-        <v>-8.7834538724206419E-06</v>
+        <v>0.00021098068627949083</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -2177,7 +2177,7 @@
         <v>0.021487848203408384</v>
       </c>
       <c r="B63">
-        <v>-1.9873968097094918E-05</v>
+        <v>0.00020304537979532939</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -2185,7 +2185,7 @@
         <v>0.020356908824281626</v>
       </c>
       <c r="B64">
-        <v>-3.1656548622980951E-05</v>
+        <v>0.0001935653918162153</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -2193,7 +2193,7 @@
         <v>0.01922596944515487</v>
       </c>
       <c r="B65">
-        <v>-4.3320311859011744E-05</v>
+        <v>0.00018308125490167405</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -2201,7 +2201,7 @@
         <v>0.018095030066028112</v>
       </c>
       <c r="B66">
-        <v>-5.40543742141204E-05</v>
+        <v>0.00017213350161123105</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -2209,7 +2209,7 @@
         <v>0.016964090686901356</v>
       </c>
       <c r="B67">
-        <v>-6.4095471504066112E-05</v>
+        <v>0.00016056423671717828</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -2217,7 +2217,7 @@
         <v>0.015833151307774598</v>
       </c>
       <c r="B68">
-        <v>-7.7870817171912763E-05</v>
+        <v>0.00014542185384287419</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -2225,7 +2225,7 @@
         <v>0.014702211928647841</v>
       </c>
       <c r="B69">
-        <v>-9.8809395132073147E-05</v>
+        <v>0.00012442021154734852</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -2233,7 +2233,7 @@
         <v>0.013571272549521085</v>
       </c>
       <c r="B70">
-        <v>-0.00012215679355705045</v>
+        <v>0.00010072873928125084</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -2241,7 +2241,7 @@
         <v>0.012440333170394329</v>
       </c>
       <c r="B71">
-        <v>-0.00014272937089083545</v>
+        <v>7.7803003462325723E-05</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -2249,7 +2249,7 @@
         <v>0.01130939379126757</v>
       </c>
       <c r="B72">
-        <v>-0.00016180996240527771</v>
+        <v>5.478754748507882E-05</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -2257,7 +2257,7 @@
         <v>0.010178454412140813</v>
       </c>
       <c r="B73">
-        <v>-0.00018154179994243081</v>
+        <v>3.025329856237617E-05</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -2265,7 +2265,7 @@
         <v>0.0090475150330140558</v>
       </c>
       <c r="B74">
-        <v>-0.00020104322479730559</v>
+        <v>4.7877422037642725E-06</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -2273,7 +2273,7 @@
         <v>0.0079165756538872988</v>
       </c>
       <c r="B75">
-        <v>-0.00021865980537823685</v>
+        <v>-2.050647199715086E-05</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -2281,7 +2281,7 @@
         <v>0.0067856362747605427</v>
       </c>
       <c r="B76">
-        <v>-0.00023267090909389829</v>
+        <v>-4.4482596407205793E-05</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -2289,7 +2289,7 @@
         <v>0.0056546968956337849</v>
       </c>
       <c r="B77">
-        <v>-0.00024148337558105727</v>
+        <v>-6.6078883214487738E-05</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -2297,7 +2297,7 @@
         <v>0.0045237575165070279</v>
       </c>
       <c r="B78">
-        <v>-0.00024408013438851641</v>
+        <v>-8.4617681931643647E-05</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -2305,7 +2305,7 @@
         <v>0.0033928181373802714</v>
       </c>
       <c r="B79">
-        <v>-0.0002387281685382048</v>
+        <v>-9.8944061278137641E-05</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -2313,7 +2313,7 @@
         <v>0.0022618787582535139</v>
       </c>
       <c r="B80">
-        <v>-0.00022238789826046007</v>
+        <v>-0.0001070320815895309</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -2321,7 +2321,7 @@
         <v>0.001130939379126757</v>
       </c>
       <c r="B81">
-        <v>-0.00018759654149985925</v>
+        <v>-0.00010390702744447922</v>
       </c>
     </row>
     <row r="82" spans="1:2">
